--- a/exports/xlsx/terms_definition_5.xlsx
+++ b/exports/xlsx/terms_definition_5.xlsx
@@ -464,8 +464,7 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGCV
-- WGISS</t>
+- WGCV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
